--- a/output/portfolio_tracker.xlsx
+++ b/output/portfolio_tracker.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -501,6 +506,11 @@
           <t>₹1,052.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹1,044.30 (-0.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>₹2,270.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹2,256.90 (-0.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -549,6 +564,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>₹1,298.50 (+0.0%)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>₹1,290.00 (-0.7%)</t>
         </is>
       </c>
     </row>
@@ -578,6 +598,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -593,6 +618,11 @@
           <t>₹1,255.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>₹1,260.60 (+0.4%)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -608,6 +638,11 @@
           <t>₹4,038.10 (+0.0%)</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>₹4,050.10 (+0.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -623,6 +658,11 @@
           <t>₹1,298.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>₹1,294.40 (-0.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -638,6 +678,11 @@
           <t>₹1,120.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>₹1,111.20 (-0.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -653,6 +698,11 @@
           <t>₹13,520.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>₹13,435.00 (-0.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -668,6 +718,11 @@
           <t>₹177.35 (+0.0%)</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>₹177.51 (+0.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -683,6 +738,11 @@
           <t>₹1,298.50 (+0.0%)</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>₹1,290.00 (-0.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -698,6 +758,11 @@
           <t>₹2,270.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>₹2,256.90 (-0.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -713,6 +778,11 @@
           <t>₹1,052.00 (+0.0%)</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>₹1,044.30 (-0.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -726,6 +796,11 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>₹270.25 (+0.0%)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>₹269.15 (-0.4%)</t>
         </is>
       </c>
     </row>

--- a/output/portfolio_tracker.xlsx
+++ b/output/portfolio_tracker.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,6 +481,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +516,11 @@
           <t>₹1,044.30 (-0.7%)</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>₹1,047.50 (+0.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,6 +551,11 @@
           <t>₹2,256.90 (-0.6%)</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>₹2,342.00 (+3.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -569,6 +584,11 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>₹1,290.00 (-0.7%)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>₹1,316.10 (+2.0%)</t>
         </is>
       </c>
     </row>
@@ -603,6 +623,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -623,6 +648,11 @@
           <t>₹1,260.60 (+0.4%)</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>₹1,265.00 (+0.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -643,6 +673,11 @@
           <t>₹4,050.10 (+0.3%)</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>₹4,045.80 (-0.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -663,6 +698,11 @@
           <t>₹1,294.40 (-0.3%)</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>₹1,287.00 (-0.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -683,6 +723,11 @@
           <t>₹1,111.20 (-0.8%)</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>₹1,144.00 (+3.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -703,6 +748,11 @@
           <t>₹13,435.00 (-0.6%)</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>₹13,376.00 (-0.4%)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -723,6 +773,11 @@
           <t>₹177.51 (+0.1%)</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>₹180.95 (+1.9%)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -743,6 +798,11 @@
           <t>₹1,290.00 (-0.7%)</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>₹1,316.10 (+2.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -763,6 +823,11 @@
           <t>₹2,256.90 (-0.6%)</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>₹2,342.00 (+3.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -783,6 +848,11 @@
           <t>₹1,044.30 (-0.7%)</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>₹1,047.50 (+0.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,6 +871,11 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>₹269.15 (-0.4%)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>₹266.00 (-1.2%)</t>
         </is>
       </c>
     </row>

--- a/output/portfolio_tracker.xlsx
+++ b/output/portfolio_tracker.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-27" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08-29" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-01" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-07" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-08" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -460,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -550,6 +552,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,6 +627,11 @@
           <t>₹1,023.40 (+0.2%)</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>₹1,005.90 (-1.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,6 +702,11 @@
           <t>₹2,320.10 (-0.9%)</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>₹2,270.00 (-2.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -760,10 +777,12 @@
           <t>₹1,319.00 (-0.9%)</t>
         </is>
       </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>₹1,282.80 (-2.7%)</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -832,6 +851,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -892,6 +916,11 @@
           <t>₹1,267.00 (+0.8%)</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>₹1,266.00 (-0.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -952,6 +981,11 @@
           <t>₹3,975.00 (-0.2%)</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>₹3,999.00 (+0.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1012,6 +1046,11 @@
           <t>₹1,302.50 (-0.4%)</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>₹1,309.50 (+0.5%)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1072,6 +1111,11 @@
           <t>₹1,130.30 (-0.3%)</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>₹1,087.50 (-3.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1132,6 +1176,11 @@
           <t>₹12,857.00 (+1.1%)</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>₹12,760.00 (-0.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1192,6 +1241,11 @@
           <t>₹175.72 (-1.2%)</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>₹172.80 (-1.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1252,6 +1306,11 @@
           <t>₹1,319.00 (-0.9%)</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>₹1,282.80 (-2.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1312,6 +1371,11 @@
           <t>₹2,320.10 (-0.9%)</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>₹2,270.00 (-2.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1372,6 +1436,11 @@
           <t>₹1,023.40 (+0.2%)</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>₹1,005.90 (-1.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1430,6 +1499,11 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>₹263.00 (-1.8%)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>₹263.50 (+0.2%)</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1521,6 +1595,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1581,6 +1660,11 @@
           <t>₹1,430.00 (+0.4%)</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>₹1,427.50 (-0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1641,10 +1725,12 @@
           <t>₹1,010.00 (+0.3%)</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>₹1,006.00 (-0.4%)</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1703,6 +1789,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1753,6 +1844,11 @@
           <t>₹421.15 (-0.1%)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>₹422.10 (+0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1803,6 +1899,11 @@
           <t>₹2,901.00 (+0.3%)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>₹2,950.00 (+1.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1853,6 +1954,11 @@
           <t>₹1,706.50 (+2.1%)</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>₹1,694.30 (-0.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1903,6 +2009,11 @@
           <t>₹7,690.00 (+1.5%)</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>₹7,672.00 (-0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1953,6 +2064,11 @@
           <t>₹5,027.00 (+0.1%)</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>₹4,995.00 (-0.6%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2003,6 +2119,11 @@
           <t>₹706.65 (+0.6%)</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>₹710.50 (+0.5%)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2053,6 +2174,11 @@
           <t>₹1,010.00 (+0.3%)</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>₹1,006.00 (-0.4%)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2103,6 +2229,11 @@
           <t>₹1,430.00 (+0.4%)</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>₹1,427.50 (-0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2153,6 +2284,11 @@
           <t>₹408.60 (+0.8%)</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>₹404.00 (-1.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2201,6 +2337,11 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>₹3,150.00 (-0.9%)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>₹3,160.00 (+0.3%)</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2292,6 +2433,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2352,6 +2498,11 @@
           <t>₹1,598.00 (-1.3%)</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>₹1,564.00 (-2.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2412,10 +2563,12 @@
           <t>₹2,320.10 (-0.9%)</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>₹2,270.00 (-2.2%)</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -2474,6 +2627,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2521,6 +2679,11 @@
           <t>₹8,692.00 (-0.1%)</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>₹8,760.00 (+0.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2571,6 +2734,11 @@
           <t>₹420.05 (+1.0%)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>₹418.85 (-0.3%)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2618,6 +2786,11 @@
           <t>₹3,310.00 (+1.2%)</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>₹3,302.40 (-0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2665,6 +2838,11 @@
           <t>₹1,308.00 (+0.3%)</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>₹1,302.00 (-0.5%)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2712,6 +2890,11 @@
           <t>₹1,715.00 (-0.9%)</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>₹1,732.00 (+1.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2759,6 +2942,11 @@
           <t>₹1,916.00 (-0.4%)</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>₹1,895.00 (-1.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2809,6 +2997,11 @@
           <t>₹2,320.10 (-0.9%)</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>₹2,270.00 (-2.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2859,6 +3052,11 @@
           <t>₹1,598.00 (-1.3%)</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>₹1,564.00 (-2.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2909,6 +3107,11 @@
           <t>₹175.72 (-1.2%)</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>₹172.80 (-1.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2957,6 +3160,11 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>₹1,319.00 (-0.9%)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>₹1,282.80 (-2.7%)</t>
         </is>
       </c>
     </row>
@@ -2971,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3028,6 +3236,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3068,6 +3281,11 @@
           <t>₹1,916.00 (-0.4%)</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>₹1,895.00 (-1.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3108,6 +3326,11 @@
           <t>₹11,920.00 (-0.7%)</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>₹11,800.00 (-1.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3148,6 +3371,11 @@
           <t>₹1,869.00 (-0.1%)</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>₹1,854.00 (-0.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3188,10 +3416,12 @@
           <t>₹1,416.00 (-0.2%)</t>
         </is>
       </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>₹1,398.00 (-1.3%)</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -3230,6 +3460,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3260,6 +3495,11 @@
           <t>₹11,920.00 (-0.7%)</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>₹11,800.00 (-1.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3290,6 +3530,11 @@
           <t>₹263.00 (-1.8%)</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>₹263.50 (+0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3320,6 +3565,11 @@
           <t>₹1,706.50 (+2.1%)</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>₹1,694.30 (-0.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3350,6 +3600,11 @@
           <t>₹12,857.00 (+1.1%)</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>₹12,760.00 (-0.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3380,6 +3635,11 @@
           <t>₹4,980.00 (+0.6%)</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>₹5,001.00 (+0.4%)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3410,6 +3670,11 @@
           <t>₹1,869.00 (-0.1%)</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>₹1,854.00 (-0.8%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3440,6 +3705,11 @@
           <t>₹1,044.20 (+0.6%)</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>₹1,037.00 (-0.7%)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3470,6 +3740,11 @@
           <t>₹1,916.00 (-0.4%)</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>₹1,895.00 (-1.1%)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3500,6 +3775,11 @@
           <t>₹421.15 (-0.1%)</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>₹422.10 (+0.2%)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3529,6 +3809,507 @@
         <is>
           <t>₹1,416.00 (-0.2%)</t>
         </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>₹1,398.00 (-1.3%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Selected Stocks — 2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Description (Sector)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Current Price (₹)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Tier(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1564</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>418.85</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Top 10 Watchlist — 2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Current Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1087.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>418.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>172.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11175</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>533.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8760</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>234.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Selected Stocks — 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Description (Sector)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Current Price (₹)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Tier(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3106</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1410.2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>413.4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Top 10 Watchlist — 2026-09-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Current Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>233.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>413.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8799</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>419.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>539.35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7690.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1410.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/portfolio_tracker.xlsx
+++ b/output/portfolio_tracker.xlsx
@@ -4116,16 +4116,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3106</v>
+        <v>411.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>233.2</v>
+        <v>1400.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1410.2</v>
+        <v>994.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4176,16 +4176,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>413.4</v>
+        <v>233.09</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4215,21 +4215,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>233.2</v>
+        <v>411.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>413.4</v>
+        <v>233.09</v>
       </c>
     </row>
     <row r="14">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8799</v>
+        <v>8824.5</v>
       </c>
     </row>
     <row r="15">
@@ -4249,17 +4249,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>419.8</v>
+        <v>419.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>539.35</v>
+        <v>237.83</v>
       </c>
     </row>
     <row r="17">
@@ -4269,47 +4269,47 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1255</v>
+        <v>1246.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3106</v>
+        <v>7728.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1020</v>
+        <v>1400.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7690.5</v>
+        <v>994.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1410.2</v>
+        <v>535.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/portfolio_tracker.xlsx
+++ b/output/portfolio_tracker.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-01" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-07" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-08" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-09" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4315,4 +4316,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Selected Stocks — 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Description (Sector)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Current Price (₹)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Tier(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>189.59</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1513.2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Top 10 Watchlist — 2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Current Price (₹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8972</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>433.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>189.59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>510.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1035.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1037.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1231.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1513.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>